--- a/main/ig/StructureDefinition-fr-lm-observation-media.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-observation-media.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T15:39:37+00:00</t>
+    <t>2026-08-05T12:15:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-observation-media.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-observation-media.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-observation-media.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-observation-media.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-observation-media.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-observation-media.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-observation-media.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-observation-media.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-observation-media.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-observation-media.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-observation-media.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-observation-media.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-observation-media.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-observation-media.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1437" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1437" uniqueCount="190">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -513,6 +513,9 @@
   </si>
   <si>
     <t>Type MIME de la piece jointe, avec encodage de caracteres, etc.</t>
+  </si>
+  <si>
+    <t>preferred</t>
   </si>
   <si>
     <t>(preferred): BCP-13</t>
@@ -4711,10 +4714,10 @@
         <v>73</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>73</v>
+        <v>162</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Z38" t="s" s="2">
         <v>73</v>
@@ -4735,7 +4738,7 @@
         <v>73</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>74</v>
@@ -4752,10 +4755,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -4781,10 +4784,10 @@
         <v>131</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -4811,10 +4814,10 @@
         <v>73</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>73</v>
+        <v>162</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Z39" t="s" s="2">
         <v>73</v>
@@ -4835,7 +4838,7 @@
         <v>73</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
@@ -4852,10 +4855,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -4878,13 +4881,13 @@
         <v>73</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -4935,7 +4938,7 @@
         <v>73</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>74</v>
@@ -4952,10 +4955,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -4978,13 +4981,13 @@
         <v>73</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5035,7 +5038,7 @@
         <v>73</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>74</v>
@@ -5052,10 +5055,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5078,13 +5081,13 @@
         <v>73</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5135,7 +5138,7 @@
         <v>73</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>74</v>
@@ -5152,10 +5155,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5178,13 +5181,13 @@
         <v>73</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5235,7 +5238,7 @@
         <v>73</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>74</v>
@@ -5252,10 +5255,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5278,13 +5281,13 @@
         <v>73</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5335,7 +5338,7 @@
         <v>73</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -5352,10 +5355,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5378,13 +5381,13 @@
         <v>73</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5435,7 +5438,7 @@
         <v>73</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>74</v>
